--- a/no_match_residual/no_match_residual_2024.xlsx
+++ b/no_match_residual/no_match_residual_2024.xlsx
@@ -583,21 +583,21 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -666,21 +666,21 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -749,21 +749,21 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -915,21 +915,21 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1164,21 +1164,21 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -1247,21 +1247,21 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -1413,21 +1413,21 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -1662,21 +1662,21 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -1745,21 +1745,21 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -1828,21 +1828,21 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -1911,21 +1911,21 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -2237,21 +2237,21 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -2318,21 +2318,21 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -2567,21 +2567,21 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -2733,21 +2733,21 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -2899,21 +2899,21 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
@@ -2982,21 +2982,21 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
@@ -3146,21 +3146,21 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -3229,21 +3229,21 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -3393,21 +3393,21 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -3476,21 +3476,21 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -3725,21 +3725,21 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -4223,21 +4223,21 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -5634,21 +5634,21 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -5966,21 +5966,21 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -6049,21 +6049,21 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
@@ -6132,21 +6132,21 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70">
@@ -6215,21 +6215,21 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71">
@@ -6298,21 +6298,21 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -6381,21 +6381,21 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73">
@@ -6464,21 +6464,21 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
@@ -6547,21 +6547,21 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -6630,21 +6630,21 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
@@ -6796,21 +6796,21 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
@@ -6879,21 +6879,21 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -7709,21 +7709,21 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
@@ -7792,21 +7792,21 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -8041,21 +8041,21 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
@@ -8124,21 +8124,21 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94">
@@ -8207,21 +8207,21 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95">
@@ -8290,21 +8290,21 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96">
@@ -8373,21 +8373,21 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97">
@@ -8456,21 +8456,21 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98">
@@ -8539,21 +8539,21 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99">
@@ -8622,21 +8622,21 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100">
@@ -8705,21 +8705,21 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101">
@@ -8788,21 +8788,21 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102">
@@ -8871,21 +8871,21 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -8954,21 +8954,21 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104">
@@ -9037,21 +9037,21 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="105">
@@ -9120,21 +9120,21 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106">
@@ -9203,21 +9203,21 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="107">
@@ -9286,21 +9286,21 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108">
@@ -9369,21 +9369,21 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109">
@@ -9452,21 +9452,21 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110">
@@ -9535,21 +9535,21 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111">
@@ -9618,21 +9618,21 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112">
@@ -9701,21 +9701,21 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113">
@@ -9784,21 +9784,21 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114">
@@ -9867,21 +9867,21 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115">
@@ -9950,21 +9950,21 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116">
@@ -10033,21 +10033,21 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117">
@@ -10116,21 +10116,21 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="118">
@@ -10199,21 +10199,21 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119">
@@ -10282,21 +10282,21 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120">
@@ -10365,21 +10365,21 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121">
@@ -10448,21 +10448,21 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122">
@@ -10531,21 +10531,21 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="123">
@@ -10614,21 +10614,21 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124">
@@ -10697,21 +10697,21 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="125">
@@ -10780,21 +10780,21 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126">
@@ -10863,21 +10863,21 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S126" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="127">
@@ -10946,21 +10946,21 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128">
@@ -11029,21 +11029,21 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129">
@@ -11112,21 +11112,21 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130">
@@ -11195,21 +11195,21 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131">
@@ -11278,21 +11278,21 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="132">
@@ -11361,21 +11361,21 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133">
@@ -11444,21 +11444,21 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S133" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134">
@@ -11527,21 +11527,21 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135">
@@ -11610,21 +11610,21 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="136">
@@ -11693,21 +11693,21 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="137">
@@ -11776,21 +11776,21 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138">
@@ -11859,21 +11859,21 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="139">
@@ -11942,21 +11942,21 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="140">
@@ -12025,21 +12025,21 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141">
@@ -12108,21 +12108,21 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142">
@@ -12191,21 +12191,21 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="143">
@@ -12274,21 +12274,21 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="144">
@@ -12357,21 +12357,21 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145">
@@ -12440,21 +12440,21 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146">
@@ -12523,21 +12523,21 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147">
@@ -12606,21 +12606,21 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S147" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148">
@@ -12689,21 +12689,21 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S148" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149">
@@ -12772,21 +12772,21 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="150">
@@ -12855,21 +12855,21 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="151">
@@ -12938,21 +12938,21 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152">
@@ -13021,21 +13021,21 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="153">
@@ -13104,21 +13104,21 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154">
@@ -13187,21 +13187,21 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155">
@@ -13270,21 +13270,21 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156">
@@ -13353,21 +13353,21 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157">
@@ -13436,21 +13436,21 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158">
@@ -13519,21 +13519,21 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="159">
@@ -13602,21 +13602,21 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="160">
@@ -13685,21 +13685,21 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161">
@@ -13768,21 +13768,21 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162">
@@ -13851,21 +13851,21 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="163">
@@ -13934,21 +13934,21 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S163" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164">
@@ -14017,21 +14017,21 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="165">
@@ -14100,21 +14100,21 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166">
@@ -14183,21 +14183,21 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="167">
@@ -14266,21 +14266,21 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168">
@@ -14349,21 +14349,21 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169">
@@ -14432,21 +14432,21 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="170">
@@ -14515,21 +14515,21 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171">
@@ -14598,21 +14598,21 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="172">
@@ -14681,21 +14681,21 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="173">
@@ -14764,21 +14764,21 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="174">
@@ -14847,21 +14847,21 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S174" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="175">
@@ -14930,21 +14930,21 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S175" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="176">
@@ -15013,21 +15013,21 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="177">
@@ -15096,21 +15096,21 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178">
@@ -15179,21 +15179,21 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179">
@@ -15262,21 +15262,21 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S179" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="180">
@@ -15345,21 +15345,21 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="181">
@@ -15428,21 +15428,21 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="182">
@@ -15511,21 +15511,21 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="183">
@@ -15594,21 +15594,21 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S183" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="184">
@@ -15677,21 +15677,21 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S184" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="185">
@@ -15760,21 +15760,21 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S185" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="186">
@@ -15843,21 +15843,21 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S186" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="187">
@@ -15926,21 +15926,21 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S187" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="188">
@@ -16009,21 +16009,21 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="189">
@@ -16092,21 +16092,21 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="190">
@@ -16175,21 +16175,21 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S190" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="191">
@@ -16258,21 +16258,21 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S191" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="192">
@@ -16341,21 +16341,21 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="193">
@@ -16424,21 +16424,21 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S193" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="194">
@@ -16507,21 +16507,21 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="195">
@@ -16590,21 +16590,21 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S195" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="196">
@@ -16673,21 +16673,21 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S196" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="197">
@@ -16756,21 +16756,21 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S197" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="198">
@@ -16839,21 +16839,21 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S198" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="199">
@@ -16922,21 +16922,21 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S199" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="200">
@@ -17005,21 +17005,21 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S200" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="201">
@@ -17088,21 +17088,21 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S201" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="202">
@@ -17171,21 +17171,21 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S202" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203">
@@ -17254,21 +17254,21 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S203" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="204">
@@ -17337,21 +17337,21 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S204" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="205">
@@ -17420,21 +17420,21 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S205" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="206">
@@ -17503,21 +17503,21 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S206" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="207">
@@ -17586,21 +17586,21 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S207" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208">
@@ -17669,21 +17669,21 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S208" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="209">
@@ -17752,21 +17752,21 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S209" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="210">
@@ -17835,21 +17835,21 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="211">
@@ -17918,21 +17918,21 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="212">
@@ -18001,21 +18001,21 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S212" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="213">
@@ -18084,21 +18084,21 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S213" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="214">
@@ -18167,21 +18167,21 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S214" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="215">
@@ -18250,21 +18250,21 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S215" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="216">
@@ -18333,21 +18333,21 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S216" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="217">
@@ -18416,21 +18416,21 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S217" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="218">
@@ -18499,21 +18499,21 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S218" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="219">
@@ -18582,21 +18582,21 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="220">
@@ -18665,21 +18665,21 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="221">
@@ -18748,21 +18748,21 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S221" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="222">
@@ -18831,21 +18831,21 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S222" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="223">
@@ -18914,21 +18914,21 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="224">
@@ -18997,21 +18997,21 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S224" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="225">
@@ -19080,21 +19080,21 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S225" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="226">
@@ -19163,21 +19163,21 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S226" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="227">
@@ -19246,21 +19246,21 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S227" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="228">
@@ -19329,21 +19329,21 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S228" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="229">
@@ -19412,21 +19412,21 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S229" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="230">
@@ -19495,21 +19495,21 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S230" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="231">
@@ -19578,21 +19578,21 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S231" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="232">
@@ -19661,21 +19661,21 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S232" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="233">
@@ -19744,21 +19744,21 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S233" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234">
@@ -19827,21 +19827,21 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S234" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="235">
@@ -19910,21 +19910,21 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S235" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="236">
@@ -19993,21 +19993,21 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S236" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="237">
@@ -20076,21 +20076,21 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S237" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="238">
@@ -20159,21 +20159,21 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S238" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="239">
@@ -20242,21 +20242,21 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S239" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="240">
@@ -20325,21 +20325,21 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S240" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="241">
@@ -20408,21 +20408,21 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S241" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="242">
@@ -20491,21 +20491,21 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S242" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="243">
@@ -20574,21 +20574,21 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S243" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="244">
@@ -20657,21 +20657,21 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S244" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="245">
@@ -20740,21 +20740,21 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S245" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="246">
@@ -20823,21 +20823,21 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S246" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="247">
@@ -20906,21 +20906,21 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S247" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="248">
@@ -20989,21 +20989,21 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S248" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="249">
@@ -21072,21 +21072,21 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S249" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="250">
@@ -21155,21 +21155,21 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S250" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="251">
@@ -21238,21 +21238,21 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S251" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="252">
@@ -21321,21 +21321,21 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S252" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="253">
@@ -21404,21 +21404,21 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S253" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="254">
@@ -21487,21 +21487,21 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S254" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="255">
@@ -21570,21 +21570,21 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S255" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="256">
@@ -21653,21 +21653,21 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S256" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="257">
@@ -21819,21 +21819,21 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S258" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="259">
@@ -23563,21 +23563,21 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S279" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="280">
@@ -23729,21 +23729,21 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="282">
@@ -23812,21 +23812,21 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S282" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="283">
@@ -23895,21 +23895,21 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S283" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="284">
@@ -26053,21 +26053,21 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S309" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="310">
@@ -26136,21 +26136,21 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S310" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="311">
@@ -26219,21 +26219,21 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S311" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="312">
@@ -26302,21 +26302,21 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S312" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="313">
@@ -26385,21 +26385,21 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S313" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
